--- a/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Océane a regardé un livre dans le salon. Ses jambes gigotent. Elle a envie de bouger. Maman dit : on va dehors. Elles mettent les chaussures. Elles prennent le ballon rouge. Elles vont au square avec maman. Dehors, le vent est doux. Un merle chante. Océane court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Océane tape le ballon. Maman le renvoie. Parce qu'elle joue dehors, son corps est content. Océane dit : je joue dehors, avec un adulte. Maman sourit. Elles jouent un moment. Océane sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Océane a pu bouger. Océane a joué dehors. Un adulte était avec elle.</t>
+          <t>Océane a regardé un livre dans le salon. Ses jambes gigotent. Elle a envie de bouger. On va dehors. Elles mettent les chaussures. Elles prennent le ballon rouge. Elles vont au square avec maman. Dehors, le vent est doux. Un merle chante. Océane court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Océane tape le ballon. Maman le renvoie. Parce qu'elle joue dehors, son corps est content. Je joue dehors, avec un adulte. Maman sourit. Elles jouent un moment. Océane sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Océane a pu bouger. Océane a joué dehors. Un adulte était avec elle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Océane a regardé un livre dans le salon. Ses jambes gigotent. Elle a envie de bouger.
+maman|On va dehors.
+narrateur|Elles mettent les chaussures. Elles prennent le ballon rouge. Elles vont au square avec maman. Dehors, le vent est doux. Un merle chante. Océane court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Océane tape le ballon. Maman le renvoie. Parce qu'elle joue dehors, son corps est content.
+enfant-f|Je joue dehors, avec un adulte. Maman sourit. Elles jouent un moment.
+narrateur|Océane sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Océane a pu bouger. Océane a joué dehors. Un adulte était avec elle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1490,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Océane veut bouger. Où joue-t-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1663,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Océane a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1826,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Océane range le ballon. Elle boit une gorgée. Merci, dit-elle à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1993,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2033,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,11 @@
 narrateur|Océane sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Océane a pu bouger. Océane a joué dehors. Un adulte était avec elle.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1497,6 +1507,7 @@
           <t>narrateur|Océane veut bouger. Où joue-t-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1668,6 +1679,7 @@
           <t>narrateur|Océane a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1831,6 +1843,7 @@
           <t>narrateur|Océane range le ballon. Elle boit une gorgée. Merci, dit-elle à maman.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1998,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2016,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2040,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Océane joue dehors au square</t>
+          <t>Le thym du square</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Le thym de la jardinière sent fort. Le banc du square est chaud. Sarah et maman y vont. Elles jouent dehors. Un adulte est là.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Océane a regardé un livre dans le salon. Ses jambes gigotent. Elle a envie de bouger. On va dehors. Elles mettent les chaussures. Elles prennent le ballon rouge. Elles vont au square avec maman. Dehors, le vent est doux. Un merle chante. Océane court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Océane tape le ballon. Maman le renvoie. Parce qu'elle joue dehors, son corps est content. Je joue dehors, avec un adulte. Maman sourit. Elles jouent un moment. Océane sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Océane a pu bouger. Océane a joué dehors. Un adulte était avec elle.</t>
+          <t>Le thym de la jardinière sent fort. Une pierre du banc est chaude. Un pigeon picore une miette. Un merle chante sur la barrière. Le trottoir est tiède sous le soleil. En ce moment, Sarah a regardé un livre. Ses jambes gigotent. Maman. J'ai envie de bouger. On va dehors. Elles mettent les chaussures. Une, puis l'autre. Elles prennent le ballon rouge. Il sent un peu le plastique. Elles vont au square. Dehors, le vent est doux. Le merle chante encore. Sarah court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Sarah tape le ballon. Maman le renvoie. Le ballon roule vers le thym. Encore ! Encore. Parce qu'elle joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Sarah. Tu bouges, et je suis là. Elles jouent un moment. Sarah sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Sarah a pu bouger. Sarah a joué dehors. Un adulte était avec elle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1329,47 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Océane a regardé un livre dans le salon. Ses jambes gigotent. Elle a envie de bouger.
+          <t>narrateur|Le thym de la jardinière sent fort.
+narrateur|Une pierre du banc est chaude.
+narrateur|Un pigeon picore une miette.
+narrateur|Un merle chante sur la barrière.
+narrateur|Le trottoir est tiède sous le soleil.
+narrateur|En ce moment, Sarah a regardé un livre.
+narrateur|Ses jambes gigotent.
+enfant-f|Maman.
+enfant-f|J'ai envie de bouger.
 maman|On va dehors.
-narrateur|Elles mettent les chaussures. Elles prennent le ballon rouge. Elles vont au square avec maman. Dehors, le vent est doux. Un merle chante. Océane court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Océane tape le ballon. Maman le renvoie. Parce qu'elle joue dehors, son corps est content.
-enfant-f|Je joue dehors, avec un adulte. Maman sourit. Elles jouent un moment.
-narrateur|Océane sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Océane a pu bouger. Océane a joué dehors. Un adulte était avec elle.</t>
+narrateur|Elles mettent les chaussures.
+narrateur|Une, puis l'autre.
+narrateur|Elles prennent le ballon rouge.
+narrateur|Il sent un peu le plastique.
+narrateur|Elles vont au square.
+narrateur|Dehors, le vent est doux.
+narrateur|Le merle chante encore.
+narrateur|Sarah court jusqu'au banc.
+narrateur|Maman reste près d'elle.
+narrateur|C'est un adulte.
+narrateur|Sarah tape le ballon.
+narrateur|Maman le renvoie.
+narrateur|Le ballon roule vers le thym.
+enfant-f|Encore !
+maman|Encore.
+narrateur|Parce qu'elle joue dehors, son corps est content.
+enfant-f|Je joue dehors, avec un adulte.
+maman|Bravo, Sarah.
+maman|Tu bouges, et je suis là.
+narrateur|Elles jouent un moment.
+narrateur|Sarah sent ses joues chaudes.
+narrateur|L'herbe sent le thym.
+narrateur|Puis elles rentrent ensemble.
+narrateur|Parce que maman était là, Sarah a pu bouger.
+narrateur|Sarah a joué dehors.
+narrateur|Un adulte était avec elle.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>enfants_parc,merle</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1396,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Océane veut bouger. Où joue-t-elle ?</t>
+          <t>Sarah veut bouger. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1552,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Océane veut bouger. Où joue-t-elle ?</t>
+          <t>narrateur|Sarah veut bouger.
+narrateur|Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Océane a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien.</t>
+          <t>Sarah a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien. Bravo. Tu as fait du bon travail. Dehors, avec un adulte. Oui, maman. Au square. Le pigeon n'est plus là. La miette non plus. Sarah pose la main sur le banc. La pierre est encore chaude. Tu as senti le thym ? Oui. Ça sent fort. Maman hoche la tête. Les joues de Sarah sont chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,7 +1725,24 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Océane a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien.</t>
+          <t>narrateur|Sarah a joué dehors.
+narrateur|Maman, un adulte, était avec elle.
+narrateur|Le corps a bougé.
+narrateur|C'est bien.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|Dehors, avec un adulte.
+enfant-f|Oui, maman.
+enfant-f|Au square.
+narrateur|Le pigeon n'est plus là.
+narrateur|La miette non plus.
+narrateur|Sarah pose la main sur le banc.
+narrateur|La pierre est encore chaude.
+maman|Tu as senti le thym ?
+enfant-f|Oui.
+enfant-f|Ça sent fort.
+narrateur|Maman hoche la tête.
+narrateur|Les joues de Sarah sont chaudes.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1704,7 +1770,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Océane range le ballon. Elle boit une gorgée. Merci, dit-elle à maman.</t>
+          <t>Sarah range le ballon. Il retrouve le couloir. Elle boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Sarah. Le merle n'est plus sur la barrière. Le vent est encore doux. On rentre les chaussures ? Oui. Sarah enlève une chaussure. Puis l'autre. Un peu de thym reste sur une semelle. Ça sent le square. On reste un peu ? Oui, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,7 +1906,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Océane range le ballon. Elle boit une gorgée. Merci, dit-elle à maman.</t>
+          <t>narrateur|Sarah range le ballon.
+narrateur|Il retrouve le couloir.
+narrateur|Elle boit une gorgée.
+narrateur|L'eau est fraîche.
+enfant-f|Merci, maman.
+maman|Merci, Sarah.
+narrateur|Le merle n'est plus sur la barrière.
+narrateur|Le vent est encore doux.
+maman|On rentre les chaussures ?
+enfant-f|Oui.
+narrateur|Sarah enlève une chaussure.
+narrateur|Puis l'autre.
+narrateur|Un peu de thym reste sur une semelle.
+enfant-f|Ça sent le square.
+maman|On reste un peu ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1868,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. Tu as fait du bon travail. Le thym a senti fort. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2089,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai joué dehors.
+enfant-f|Avec un adulte.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+maman|Le thym a senti fort.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2154,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le thym de la jardinière sent fort. Une pierre du banc est chaude. Un pigeon picore une miette. Un merle chante sur la barrière. Le trottoir est tiède sous le soleil. En ce moment, Sarah a regardé un livre. Ses jambes gigotent. Maman. J'ai envie de bouger. On va dehors. Elles mettent les chaussures. Une, puis l'autre. Elles prennent le ballon rouge. Il sent un peu le plastique. Elles vont au square. Dehors, le vent est doux. Le merle chante encore. Sarah court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Sarah tape le ballon. Maman le renvoie. Le ballon roule vers le thym. Encore ! Encore. Parce qu'elle joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Sarah. Tu bouges, et je suis là. Elles jouent un moment. Sarah sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Sarah a pu bouger. Sarah a joué dehors. Un adulte était avec elle.</t>
+          <t>Le thym de la jardinière sent fort. Une pierre du banc est chaude. Un pigeon picore une miette. Un merle chante sur la barrière. Le trottoir est tiède sous le soleil. Dans le salon, un livre est ouvert. Une page jaune attend. En ce moment, Sarah ferme le livre. Ses jambes gigotent. Maman. J'ai envie de bouger. On va dehors. Elles mettent les chaussures. Une, puis l'autre. Elles prennent le ballon rouge. Il sent un peu le plastique. Elles vont au square. Dehors, le vent est doux. Le merle chante encore. Sarah court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Sarah tape le ballon. Maman le renvoie. Le ballon roule vers le thym. Encore ! Encore. Parce qu'elle joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Sarah. Tu bouges, et je suis là. Tu as fini de taper le ballon ? Encore un peu. Encore un peu, d'accord. Elles jouent un moment. Sarah sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Je suis avec toi, Sarah. Oui, maman. Sarah donne la main. Sarah a joué dehors. Un adulte était avec elle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Océane a regardé un livre dans le salon. Ses jambes gigotent. Elle a envie de bouger. Maman dit : on va &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Elles mettent les chaussures. Elles prennent le ballon rouge. Elles vont au square avec maman. Dehors, le vent est doux. Un merle chante. Océane court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Océane tape le ballon. Maman le renvoie. Parce qu'elle joue dehors, son corps est content. Océane dit : je joue dehors, avec un adulte. Maman sourit. Elles jouent un moment. Océane sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Parce que maman était là, Océane a pu bouger. Océane a joué dehors. Un adulte était avec elle.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le thym de la jardinière sent fort. Une pierre du banc est chaude. Un pigeon picore une miette. Un merle chante sur la barrière. Le trottoir est tiède sous le soleil. Dans le salon, un livre est ouvert. Une page jaune attend. En ce moment, Sarah ferme le livre. Ses jambes gigotent. Maman. J'ai envie de bouger. On va dehors. Elles mettent les chaussures. Une, puis l'autre. Elles prennent le ballon rouge. Il sent un peu le plastique. Elles vont au square. Dehors, le vent est doux. Le merle chante encore. Sarah court jusqu'au banc. Maman reste près d'elle. C'est un adulte. Sarah tape le ballon. Maman le renvoie. Le ballon roule vers le thym. Encore ! Encore. Parce qu'elle joue dehors, son corps est content. Je joue dehors, avec un adulte. Bravo, Sarah. Tu bouges, et je suis là. Tu as fini de taper le ballon ? Encore un peu. Encore un peu, d'accord. Elles jouent un moment. Sarah sent ses joues chaudes. L'herbe sent le thym. Puis elles rentrent ensemble. Je suis avec toi, Sarah. Oui, maman. Sarah donne la main. Sarah a joué dehors. Un adulte était avec elle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1334,7 +1334,9 @@
 narrateur|Un pigeon picore une miette.
 narrateur|Un merle chante sur la barrière.
 narrateur|Le trottoir est tiède sous le soleil.
-narrateur|En ce moment, Sarah a regardé un livre.
+narrateur|Dans le salon, un livre est ouvert.
+narrateur|Une page jaune attend.
+narrateur|En ce moment, Sarah ferme le livre.
 narrateur|Ses jambes gigotent.
 enfant-f|Maman.
 enfant-f|J'ai envie de bouger.
@@ -1358,11 +1360,16 @@
 enfant-f|Je joue dehors, avec un adulte.
 maman|Bravo, Sarah.
 maman|Tu bouges, et je suis là.
+maman|Tu as fini de taper le ballon ?
+enfant-f|Encore un peu.
+maman|Encore un peu, d'accord.
 narrateur|Elles jouent un moment.
 narrateur|Sarah sent ses joues chaudes.
 narrateur|L'herbe sent le thym.
 narrateur|Puis elles rentrent ensemble.
-narrateur|Parce que maman était là, Sarah a pu bouger.
+maman|Je suis avec toi, Sarah.
+enfant-f|Oui, maman.
+narrateur|Sarah donne la main.
 narrateur|Sarah a joué dehors.
 narrateur|Un adulte était avec elle.</t>
         </is>
@@ -1401,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Océane veut bouger. Où joue-t-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah veut bouger. Où joue-t-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1556,7 +1563,6 @@
 narrateur|Où joue-t-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1581,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien. Bravo. Tu as fait du bon travail. Dehors, avec un adulte. Oui, maman. Au square. Le pigeon n'est plus là. La miette non plus. Sarah pose la main sur le banc. La pierre est encore chaude. Tu as senti le thym ? Oui. Ça sent fort. Maman hoche la tête. Les joues de Sarah sont chaudes.</t>
+          <t>Sarah a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien. Bravo. Dehors, avec un adulte. Oui, maman. Au square. Le pigeon n'est plus là. La miette non plus. Sarah pose la main sur le banc. La pierre est encore chaude. Tu as senti le thym ? Oui. Ça sent fort. Oui. Ça sent le square. Les joues de Sarah sont chaudes.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Océane a joué &lt;emphasis level="moderate"&gt;dehors&lt;/emphasis&gt;. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a joué dehors. Maman, un adulte, était avec elle. Le corps a bougé. C'est bien. Bravo. Dehors, avec un adulte. Oui, maman. Au square. Le pigeon n'est plus là. La miette non plus. Sarah pose la main sur le banc. La pierre est encore chaude. Tu as senti le thym ? Oui. Ça sent fort. Oui. Ça sent le square. Les joues de Sarah sont chaudes.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1730,7 +1736,6 @@
 narrateur|Le corps a bougé.
 narrateur|C'est bien.
 maman|Bravo.
-maman|Tu as fait du bon travail.
 maman|Dehors, avec un adulte.
 enfant-f|Oui, maman.
 enfant-f|Au square.
@@ -1741,11 +1746,11 @@
 maman|Tu as senti le thym ?
 enfant-f|Oui.
 enfant-f|Ça sent fort.
-narrateur|Maman hoche la tête.
+maman|Oui.
+maman|Ça sent le square.
 narrateur|Les joues de Sarah sont chaudes.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1770,12 +1775,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Sarah range le ballon. Il retrouve le couloir. Elle boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Sarah. Le merle n'est plus sur la barrière. Le vent est encore doux. On rentre les chaussures ? Oui. Sarah enlève une chaussure. Puis l'autre. Un peu de thym reste sur une semelle. Ça sent le square. On reste un peu ? Oui, maman.</t>
+          <t>Sarah range le ballon. Il retrouve le couloir. Elle boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Sarah. Le merle n'est plus sur la barrière. Le vent est encore doux. On rentre les chaussures ? Oui. Sarah enlève une chaussure. Puis l'autre. Un peu de thym reste sur une semelle. Ça sent le square. On reste un peu ? Oui, maman. Le livre attend sur la table. La page jaune, on la lira plus tard. D'accord. Le thym sent encore, tout doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Océane range le ballon. Elle boit une gorgée. Merci, dit-elle à maman.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah range le ballon. Il retrouve le couloir. Elle boit une gorgée. L'eau est fraîche. Merci, maman. Merci, Sarah. Le merle n'est plus sur la barrière. Le vent est encore doux. On rentre les chaussures ? Oui. Sarah enlève une chaussure. Puis l'autre. Un peu de thym reste sur une semelle. Ça sent le square. On reste un peu ? Oui, maman. Le livre attend sur la table. La page jaune, on la lira plus tard. D'accord. Le thym sent encore, tout doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1921,10 +1926,13 @@
 narrateur|Un peu de thym reste sur une semelle.
 enfant-f|Ça sent le square.
 maman|On reste un peu ?
-enfant-f|Oui, maman.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+enfant-f|Oui, maman.
+narrateur|Le livre attend sur la table.
+maman|La page jaune, on la lira plus tard.
+enfant-f|D'accord.
+narrateur|Le thym sent encore, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,12 +1957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai joué dehors. Avec un adulte. Bravo. Tu as fait du bon travail. Le thym a senti fort. L'histoire est finie.</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. Le thym a senti fort.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai joué dehors. Avec un adulte. Bravo. Le thym a senti fort.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,12 +2100,9 @@
           <t>enfant-f|J'ai joué dehors.
 enfant-f|Avec un adulte.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-maman|Le thym a senti fort.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Le thym a senti fort.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2116,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2161,6 +2166,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
+++ b/stories/arbres/ATOM-SAN.MOV.001-03.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Océane, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
